--- a/flow.xlsx
+++ b/flow.xlsx
@@ -20,39 +20,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+  <si>
+    <t xml:space="preserve">I &lt;= n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p *= I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i+=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p = 1*1 = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p = 1*2 = 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p = 2*3= 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p = 6*4 = 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p = 24*5 = 120</t>
+  </si>
   <si>
     <t xml:space="preserve">p = 1</t>
   </si>
   <si>
+    <t xml:space="preserve">f</t>
+  </si>
+  <si>
     <t xml:space="preserve">I = 1</t>
   </si>
   <si>
     <t xml:space="preserve">n = input → 5(say)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I &lt;= n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p *= I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i+=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p = 1*1 = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p = 1*2 = 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p = 2*3= 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p = 6*4 = 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p = 24*5 = 120</t>
   </si>
 </sst>
 </file>
@@ -67,6 +70,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -88,6 +92,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -151,33 +156,37 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -363,104 +372,125 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:D12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>3</v>
+      <c r="A8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>4</v>
+      <c r="A9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="C11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="C12" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/flow.xlsx
+++ b/flow.xlsx
@@ -372,9 +372,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.75"/>
   </cols>
   <sheetData>
@@ -458,7 +459,7 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -469,7 +470,7 @@
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -478,15 +479,9 @@
         <v>11</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="1">
